--- a/Day-09-Filtering-Sorting/Day-09-Filtering-Sorting.xlsx
+++ b/Day-09-Filtering-Sorting/Day-09-Filtering-Sorting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\90_Day_Data_Analytics\Day-09-Filtering-Sorting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B234ABF-405D-4037-B408-2DF211642C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F98D9-1099-4F29-8350-0870C16127F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{8B06867D-941F-48E8-BB7A-568E2E317053}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="21">
   <si>
     <t>Order_ID</t>
   </si>
@@ -170,11 +170,18 @@
       <t>?</t>
     </r>
   </si>
+  <si>
+    <t>Average</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -253,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -268,6 +275,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,6 +606,7 @@
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" customWidth="1"/>
     <col min="9" max="9" width="37.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
@@ -621,7 +639,7 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="8">
         <v>55000</v>
       </c>
     </row>
@@ -635,7 +653,7 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="8">
         <v>18000</v>
       </c>
       <c r="I3" t="s">
@@ -652,7 +670,7 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="8">
         <v>3000</v>
       </c>
     </row>
@@ -666,9 +684,10 @@
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="8">
         <v>4000</v>
       </c>
+      <c r="E5" s="9"/>
       <c r="I5" t="s">
         <v>16</v>
       </c>
@@ -683,7 +702,7 @@
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="8">
         <v>2500</v>
       </c>
     </row>
@@ -697,7 +716,7 @@
       <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="8">
         <v>15000</v>
       </c>
       <c r="I7" t="s">
@@ -714,11 +733,14 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="8">
         <v>8000</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
@@ -727,6 +749,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E10" s="7">
+        <f>AVERAGE(D2:D8)</f>
+        <v>15071.428571428571</v>
+      </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
@@ -763,7 +789,7 @@
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="8">
         <v>55000</v>
       </c>
     </row>
@@ -777,7 +803,7 @@
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -843,7 +869,7 @@
       <c r="C19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="8">
         <v>2500</v>
       </c>
     </row>
@@ -943,7 +969,7 @@
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="8">
         <v>55000</v>
       </c>
       <c r="G26" s="2">
@@ -955,7 +981,7 @@
       <c r="I26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="8">
         <v>55000</v>
       </c>
     </row>
@@ -969,7 +995,7 @@
       <c r="C27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="8">
         <v>18000</v>
       </c>
       <c r="G27" s="2">
@@ -981,7 +1007,7 @@
       <c r="I27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="8">
         <v>18000</v>
       </c>
     </row>
@@ -995,7 +1021,7 @@
       <c r="C28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="8">
         <v>15000</v>
       </c>
       <c r="G28" s="2">
@@ -1007,7 +1033,7 @@
       <c r="I28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="8">
         <v>15000</v>
       </c>
     </row>
@@ -1021,7 +1047,7 @@
       <c r="C29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="8">
         <v>8000</v>
       </c>
       <c r="G29" s="2">
@@ -1033,7 +1059,7 @@
       <c r="I29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="8">
         <v>8000</v>
       </c>
     </row>
@@ -1047,7 +1073,7 @@
       <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="8">
         <v>4000</v>
       </c>
       <c r="G30" s="2">
@@ -1059,7 +1085,7 @@
       <c r="I30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="8">
         <v>4000</v>
       </c>
     </row>
@@ -1073,7 +1099,7 @@
       <c r="C31" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="8">
         <v>3000</v>
       </c>
       <c r="G31" s="2">
@@ -1085,11 +1111,11 @@
       <c r="I31" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="8">
         <v>3000</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>105</v>
       </c>
@@ -1099,7 +1125,7 @@
       <c r="C32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="8">
         <v>2500</v>
       </c>
       <c r="G32" s="2">
@@ -1111,7 +1137,7 @@
       <c r="I32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="8">
         <v>2500</v>
       </c>
     </row>
